--- a/docs/StructureDefinition-DebtPortalChargeItemremoved.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemremoved.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemremoved.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemremoved.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemremoved.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemremoved.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemremoved.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemremoved.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -723,10 +723,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpci-27-2029:If NOT NULL and INTEGRATED BILLING ACTION - PARENT CHARGE (350-.09) &lt;&gt; INTEGRATED BILLING ACTION - IEN (350-.001) then source value from (350-.1 &gt; 350.3-.01) {true}</t>
-  </si>
-  <si>
-    <t>2029: source value based on INTEGRATED BILLING ACTION - CANCELLATION REASON &gt; IB CHARGE REMOVE REASONS - NAME (350-.1 &gt; 350.3-.01) if NOT NULL and INTEGRATED BILLING ACTION - PARENT CHARGE (350-.09) &lt;&gt; INTEGRATED BILLING ACTION - IEN (350-.001)</t>
+dpci-27-2029:If NOT NULL and  INTEGRATED BILLING ACTION - PARENT CHARGE (350-.09) &lt;&gt; INTEGRATED BILLING ACTION - IEN (350-.001) then source value from (350-.1 &gt; 350.3-.01) {true}</t>
+  </si>
+  <si>
+    <t>2029: source value based on INTEGRATED BILLING ACTION - CANCELLATION REASON &gt; IB CHARGE REMOVE REASONS - NAME (350-.1 &gt; 350.3-.01) if NOT NULL and  INTEGRATED BILLING ACTION - PARENT CHARGE (350-.09) &lt;&gt; INTEGRATED BILLING ACTION - IEN (350-.001)</t>
   </si>
   <si>
     <t>IB.IBAction.IBChargeRemoveReasonIEN
@@ -1565,7 +1565,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="253.421875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="254.00390625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="49.5078125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
